--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep/param_p99_heatmap_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep/param_p99_heatmap_1Mbps.xlsx
@@ -560,29 +560,17 @@
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>9102</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>11502</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>9652</v>
-      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>9102</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>11232</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>10808</v>
-      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -590,29 +578,17 @@
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>9498</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>11538</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>9952</v>
-      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>10172</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>8272</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>10068</v>
-      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -620,29 +596,17 @@
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>10982</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>10892</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>10172</v>
-      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>8258</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>11488</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>10542</v>
-      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -650,29 +614,17 @@
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>10788</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>8492</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>9142</v>
-      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>10798</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>10222</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>9888</v>
-      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -680,29 +632,17 @@
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>8812</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>8388</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>9798</v>
-      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>9842</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>9232</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>10318</v>
-      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -710,29 +650,17 @@
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>10092</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>10872</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>10472</v>
-      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>9702</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>9792</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>10568</v>
-      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -789,29 +717,17 @@
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>10408</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>10232</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>8178</v>
-      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>10408</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>9152</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>8292</v>
-      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -819,29 +735,17 @@
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>9578</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>8752</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>9048</v>
-      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>10048</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>9918</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>9698</v>
-      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -849,29 +753,17 @@
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>9048</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>8712</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>8622</v>
-      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>11012</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>8392</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>9358</v>
-      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -879,29 +771,17 @@
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>9408</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>11408</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>10382</v>
-      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>9732</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>9532</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>9982</v>
-      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -909,29 +789,17 @@
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>9022</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>12092</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>8272</v>
-      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>9218</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>9868</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>9878</v>
-      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -939,29 +807,17 @@
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>11822</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>11802</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>8872</v>
-      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>9532</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>10712</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>11088</v>
-      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1018,29 +874,17 @@
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
-        <v>10882</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>10122</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>7422</v>
-      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>10882</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>10312</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>8062</v>
-      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1048,29 +892,17 @@
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>11938</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>9752</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>5632</v>
-      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>11328</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>9218</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>5552</v>
-      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1078,29 +910,17 @@
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>10928</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>7902</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>8028</v>
-      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
-        <v>9482</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>7628</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>7978</v>
-      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1108,29 +928,17 @@
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>10178</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>8222</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>8212</v>
-      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
-        <v>8318</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>8278</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>8282</v>
-      </c>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1138,29 +946,17 @@
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
-        <v>8258</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>8442</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>9398</v>
-      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
-        <v>11232</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>8712</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>9178</v>
-      </c>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1168,29 +964,17 @@
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>8648</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>8548</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>9018</v>
-      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>10338</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>9348</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>8338</v>
-      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1359,13 +1143,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>10238</v>
+        <v>9322</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7568</v>
+        <v>6122</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6148</v>
+        <v>75362</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1373,13 +1157,13 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>10238</v>
+        <v>9322</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>6102</v>
+        <v>6328</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5118</v>
+        <v>75362</v>
       </c>
     </row>
     <row r="6">
@@ -1389,13 +1173,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9088</v>
+        <v>11568</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7358</v>
+        <v>6122</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5342</v>
+        <v>6032</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1403,13 +1187,13 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9872</v>
+        <v>11822</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>5752</v>
+        <v>6142</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>81248</v>
+        <v>294222</v>
       </c>
     </row>
     <row r="7">
@@ -1419,13 +1203,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8858</v>
+        <v>8272</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7732</v>
+        <v>7988</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7682</v>
+        <v>7778</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1433,13 +1217,13 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>7698</v>
+        <v>9592</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8018</v>
+        <v>8022</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>7782</v>
+        <v>7778</v>
       </c>
     </row>
     <row r="8">
@@ -1449,13 +1233,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>9092</v>
+        <v>8778</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8062</v>
+        <v>8288</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>8038</v>
+        <v>8312</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1463,13 +1247,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8952</v>
+        <v>8802</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8182</v>
+        <v>8342</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>8042</v>
+        <v>8218</v>
       </c>
     </row>
     <row r="9">
@@ -1479,13 +1263,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8232</v>
+        <v>8772</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>8088</v>
+        <v>8328</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8188</v>
+        <v>8342</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -1493,13 +1277,13 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8338</v>
+        <v>8312</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>8228</v>
+        <v>8268</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>8288</v>
+        <v>8172</v>
       </c>
     </row>
     <row r="10">
@@ -1509,13 +1293,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>8502</v>
+        <v>10802</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>8482</v>
+        <v>8568</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>8602</v>
+        <v>8632</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -1523,13 +1307,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8342</v>
+        <v>9402</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8322</v>
+        <v>9188</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>8312</v>
+        <v>9588</v>
       </c>
     </row>
     <row r="12">
@@ -1588,13 +1372,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>10792</v>
+        <v>11282</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7958</v>
+        <v>8888</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4368</v>
+        <v>6688</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -1602,13 +1386,13 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>10792</v>
+        <v>11282</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>7142</v>
+        <v>7742</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>4872</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="15">
@@ -1618,13 +1402,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>9718</v>
+        <v>11252</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>6018</v>
+        <v>6762</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6198</v>
+        <v>6918</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -1632,13 +1416,13 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>9652</v>
+        <v>10498</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7212</v>
+        <v>7328</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>5952</v>
+        <v>5832</v>
       </c>
     </row>
     <row r="16">
@@ -1648,13 +1432,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>8448</v>
+        <v>11128</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>7728</v>
+        <v>7982</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>7662</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1662,13 +1446,13 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>9868</v>
+        <v>10328</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>7642</v>
+        <v>8172</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>7698</v>
+        <v>7858</v>
       </c>
     </row>
     <row r="17">
@@ -1678,13 +1462,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>8292</v>
+        <v>10922</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>8332</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8288</v>
+        <v>8202</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1692,13 +1476,13 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>8498</v>
+        <v>8432</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>8178</v>
+        <v>8252</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>8182</v>
+        <v>8208</v>
       </c>
     </row>
     <row r="18">
@@ -1708,13 +1492,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>8322</v>
+        <v>9302</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>9422</v>
+        <v>8402</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8208</v>
+        <v>10802</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1722,13 +1506,13 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>8378</v>
+        <v>9172</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>8328</v>
+        <v>8362</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>8512</v>
+        <v>8372</v>
       </c>
     </row>
     <row r="19">
@@ -1738,13 +1522,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>11958</v>
+        <v>9212</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13158</v>
+        <v>8838</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>8548</v>
+        <v>9388</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1752,13 +1536,13 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9132</v>
+        <v>9552</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9368</v>
+        <v>10008</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>10038</v>
+        <v>8692</v>
       </c>
     </row>
     <row r="21">
@@ -1817,13 +1601,13 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>11072</v>
+        <v>11082</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>10148</v>
+        <v>11432</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8338</v>
+        <v>10522</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1831,13 +1615,13 @@
         </is>
       </c>
       <c r="G23" s="6" t="n">
-        <v>11072</v>
+        <v>11082</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>10338</v>
+        <v>10182</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>8658</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="24">
@@ -1847,13 +1631,13 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>12108</v>
+        <v>12708</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>9882</v>
+        <v>11148</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5932</v>
+        <v>6308</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -1861,13 +1645,13 @@
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>11432</v>
+        <v>12788</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>9332</v>
+        <v>11232</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5808</v>
+        <v>9392</v>
       </c>
     </row>
     <row r="25">
@@ -1877,13 +1661,13 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>11018</v>
+        <v>9528</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>7912</v>
+        <v>7808</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>8108</v>
+        <v>8252</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -1891,13 +1675,13 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>9528</v>
+        <v>10768</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>7632</v>
+        <v>8358</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8062</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="26">
@@ -1907,13 +1691,13 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>10188</v>
+        <v>10102</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>8228</v>
+        <v>8368</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>8242</v>
+        <v>8362</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1921,13 +1705,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>8322</v>
+        <v>8862</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>8282</v>
+        <v>8962</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8298</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="27">
@@ -1937,13 +1721,13 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8262</v>
+        <v>14382</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>8448</v>
+        <v>12868</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9752</v>
+        <v>9058</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -1951,13 +1735,13 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>11262</v>
+        <v>10642</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>8718</v>
+        <v>14552</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>9588</v>
+        <v>13978</v>
       </c>
     </row>
     <row r="28">
@@ -1967,13 +1751,13 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>8652</v>
+        <v>10272</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>8568</v>
+        <v>10688</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9058</v>
+        <v>14508</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -1981,13 +1765,13 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>10342</v>
+        <v>10278</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>9392</v>
+        <v>9028</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>8342</v>
+        <v>15088</v>
       </c>
     </row>
   </sheetData>
@@ -2157,13 +1941,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>8898</v>
+        <v>8358</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>11808</v>
+        <v>11958</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>9892</v>
+        <v>9778</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -2171,13 +1955,13 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8898</v>
+        <v>8358</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>11552</v>
+        <v>11762</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>11102</v>
+        <v>8832</v>
       </c>
     </row>
     <row r="6">
@@ -2187,13 +1971,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9618</v>
+        <v>12312</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11818</v>
+        <v>11242</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10438</v>
+        <v>11222</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -2201,13 +1985,13 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>10192</v>
+        <v>11578</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>8332</v>
+        <v>10262</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10538</v>
+        <v>11532</v>
       </c>
     </row>
     <row r="7">
@@ -2217,13 +2001,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>11298</v>
+        <v>11792</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>11468</v>
+        <v>13472</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10692</v>
+        <v>11768</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -2231,13 +2015,13 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8318</v>
+        <v>12168</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>11972</v>
+        <v>13392</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>11212</v>
+        <v>11712</v>
       </c>
     </row>
     <row r="8">
@@ -2247,13 +2031,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>11032</v>
+        <v>9838</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8768</v>
+        <v>11822</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>9602</v>
+        <v>11688</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -2261,13 +2045,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>11068</v>
+        <v>9978</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>10758</v>
+        <v>12558</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10568</v>
+        <v>11052</v>
       </c>
     </row>
     <row r="9">
@@ -2277,13 +2061,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>9112</v>
+        <v>12178</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>8822</v>
+        <v>11078</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10428</v>
+        <v>11632</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2291,13 +2075,13 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>10168</v>
+        <v>11238</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>9698</v>
+        <v>9618</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>10808</v>
+        <v>9268</v>
       </c>
     </row>
     <row r="10">
@@ -2307,13 +2091,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>10422</v>
+        <v>13162</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>11172</v>
+        <v>10902</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>10692</v>
+        <v>11158</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2321,13 +2105,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9932</v>
+        <v>11398</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>10118</v>
+        <v>11962</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>10942</v>
+        <v>11862</v>
       </c>
     </row>
     <row r="12">
@@ -2386,13 +2170,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>10278</v>
+        <v>10338</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>10678</v>
+        <v>11938</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8268</v>
+        <v>10642</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -2400,13 +2184,13 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>10278</v>
+        <v>10338</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>9592</v>
+        <v>10638</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>8732</v>
+        <v>10728</v>
       </c>
     </row>
     <row r="15">
@@ -2416,13 +2200,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>9552</v>
+        <v>12228</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>9488</v>
+        <v>12348</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>9682</v>
+        <v>12318</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -2430,13 +2214,13 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>10362</v>
+        <v>10482</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>10512</v>
+        <v>12568</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>10588</v>
+        <v>8618</v>
       </c>
     </row>
     <row r="16">
@@ -2446,13 +2230,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>9498</v>
+        <v>12228</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>9848</v>
+        <v>11342</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>9978</v>
+        <v>12292</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2460,13 +2244,13 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>11692</v>
+        <v>11698</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>10162</v>
+        <v>12758</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>10838</v>
+        <v>10612</v>
       </c>
     </row>
     <row r="17">
@@ -2476,13 +2260,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>10242</v>
+        <v>13438</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>12678</v>
+        <v>12188</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>11742</v>
+        <v>10812</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2490,13 +2274,13 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>10528</v>
+        <v>11408</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>11058</v>
+        <v>11618</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>11838</v>
+        <v>12058</v>
       </c>
     </row>
     <row r="18">
@@ -2506,13 +2290,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>9758</v>
+        <v>10498</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12968</v>
+        <v>10898</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8432</v>
+        <v>12588</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2520,13 +2304,13 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>9968</v>
+        <v>11352</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>11102</v>
+        <v>10712</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>10752</v>
+        <v>10538</v>
       </c>
     </row>
     <row r="19">
@@ -2536,13 +2320,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>11768</v>
+        <v>10258</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>11528</v>
+        <v>9918</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>9288</v>
+        <v>10932</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2550,13 +2334,13 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9878</v>
+        <v>10572</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>11342</v>
+        <v>11098</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>11392</v>
+        <v>10348</v>
       </c>
     </row>
   </sheetData>

--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep/param_p99_heatmap_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep/param_p99_heatmap_1Mbps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All STAs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P-EDCA STAs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy STAs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All STAs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P-EDCA STAs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legacy STAs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,11 +34,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0079C0FF"/>
+      <color rgb="00E3B341"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00E3B341"/>
+      <color rgb="0079C0FF"/>
     </font>
     <font>
       <b val="1"/>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -106,7 +106,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -484,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -501,7 +504,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>All STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>All STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -515,475 +518,2095 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>2052</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>2322</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>2308</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2288</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>2248</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>2398</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>2622</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>2762</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2822</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>2628</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>2832</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2902</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2852</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>2692</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>2552</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2648</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2568</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>2168</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2362</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2368</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2402</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>2378</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2362</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2452</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>8042</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>8038</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>7968</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>8088</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>8088</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>7998</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>7992</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>7998</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>8148</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>7908</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>7948</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>8012</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>7922</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>8022</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>8068</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>8068</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>8058</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>8048</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>8038</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>7882</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>8018</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>7988</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>7708</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>7922</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>7922</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>7908</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>7932</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>7918</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>7958</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>8018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>11678</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>11852</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>11812</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="n">
+        <v>11678</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>11708</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>11638</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>11612</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>11612</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="n">
+        <v>11428</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>11978</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>11448</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="n">
+        <v>11258</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>11282</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>11528</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>11198</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>11608</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>11628</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>11438</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>11562</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>11502</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="n">
+        <v>11352</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>10838</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>11372</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>11212</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>11458</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>11128</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="n">
+        <v>10258</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>10838</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>11452</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="n">
+        <v>10922</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>10972</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>10942</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
+      <c r="G29" s="7" t="n">
+        <v>10932</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>10968</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>11228</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1932</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>2162</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2222</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2208</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2122</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2248</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>2932</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>3108</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>3118</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>3042</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>3128</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>3352</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>3128</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>3262</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>3472</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>3212</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>3388</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>2752</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2708</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>2532</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2628</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2682</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>2428</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2572</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2318</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2478</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2522</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>8112</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>8118</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>8112</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>8118</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>7958</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>8138</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>8152</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>8028</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>7932</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>8022</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>8068</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>8018</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>7938</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>8052</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>8058</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>8182</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>8068</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>8098</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>8072</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>7992</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>8082</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>8062</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>7988</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>8012</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>7908</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>7992</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>8022</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>8008</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>12518</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>12588</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>12928</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>12518</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>13062</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>12772</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>12232</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>12562</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>12402</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>12028</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>12282</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>12768</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>11752</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>12152</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>12142</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>11998</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>11982</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>12512</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>11662</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>11828</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>12198</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>11722</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>12098</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>12042</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>11552</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>11678</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>11462</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>11222</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>11658</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>11678</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>11148</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>11358</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>11062</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>11272</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>11522</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>11598</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>2092</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>2148</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2172</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>2222</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>3118</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>3312</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>3282</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>2988</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>3322</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>3662</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>3562</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>3648</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>3432</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>3778</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>2752</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>2732</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>2752</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2772</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>2762</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2338</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2372</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>2502</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>2422</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>2482</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>8248</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>7982</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>7662</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>8222</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>8132</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>8138</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>8128</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>8152</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>7958</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>7832</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>7838</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>8078</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>8142</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>8108</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>8158</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>8062</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>8122</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>8082</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>8062</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>8108</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>8058</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>8058</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>7888</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>7918</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>7968</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>7942</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>7912</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>12718</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>13098</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>13352</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>12718</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>13108</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>12452</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>12502</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>12828</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>12772</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>12618</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>13212</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>13512</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>12342</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>12708</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>12762</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>11862</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>12358</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>13092</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>12388</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>12288</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>12602</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>12062</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>12522</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>12452</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>11938</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>11838</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>12258</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>11672</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>12168</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>11918</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>11032</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>11192</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>11422</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>11342</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>11408</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>11338</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -995,7 +2618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1007,7 +2630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1019,7 +2642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1031,7 +2654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:D28">
+  <conditionalFormatting sqref="B24:D29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1043,8 +2666,152 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:I28">
+  <conditionalFormatting sqref="G24:I29">
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:D69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:I69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D78">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:I78">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:D87">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:I87">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1066,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1083,7 +2850,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P-EDCA STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>P-EDCA STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -1097,691 +2864,2095 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>9322</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>6122</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>75362</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1392</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>9322</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>6328</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>75362</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>1372</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1392</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>11568</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>6122</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>6032</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>11822</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>6142</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>294222</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1888</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>8272</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>7988</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>7778</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>2812</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>2998</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>3138</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>9592</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>8022</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>7778</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>2768</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>3132</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>8778</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>8288</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>8312</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>3722</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>3638</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>8802</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>8342</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>8218</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>3398</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>3452</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>3622</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>8772</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>8328</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>8342</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>2558</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2592</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>8312</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>8268</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>8172</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2278</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>10802</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>8632</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>2058</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>9402</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>9188</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>9588</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>11282</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>8888</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>6688</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>6608</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>5522</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>5302</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>11282</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>7742</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>6248</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>6608</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>5122</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>11252</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>6762</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>6918</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>6298</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>5612</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5302</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>10498</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>7328</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>5832</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>6142</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>5272</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>4778</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>11128</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>7982</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>7948</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>6722</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>6612</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>6658</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>10328</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>8172</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>7858</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>6722</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>6598</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>6552</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>10922</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>8332</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>8202</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>7632</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>7678</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>7612</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>8432</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>8252</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>8208</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>7638</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>7542</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>7638</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>8402</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>10802</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>7832</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>7752</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>7718</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>9172</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>8362</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>8372</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>7658</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>7738</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>7802</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>9212</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>8838</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>9388</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>7752</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>7692</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>7668</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>9552</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>10008</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>8692</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>7728</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>7658</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>7682</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
-        <v>11082</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>11432</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>10522</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>9662</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>8322</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>8868</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>11082</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>10182</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>11028</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="n">
+        <v>9662</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>8228</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B25" s="7" t="n">
+        <v>9668</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>8568</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>9382</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>8358</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>7722</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>9318</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>8328</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>8338</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>9258</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>8218</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>9442</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>8612</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>8292</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>9648</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>8262</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>8252</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>9512</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>8278</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>8448</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>8272</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>8272</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>9238</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>8312</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>8272</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>9078</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>8288</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>8252</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1582</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1632</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1582</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1918</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>3048</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>3242</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>3258</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>3132</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>3192</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>3472</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>3442</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>3608</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>3562</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>3708</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>2758</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2592</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>2448</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2618</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2518</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>2282</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2128</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2348</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2292</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>7528</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>7302</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>7258</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>7528</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>7202</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>6768</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>7612</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>7418</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>7418</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>7422</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>6938</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>7002</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>7432</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>7508</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>7442</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>7482</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>7028</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>7408</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>7878</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>7848</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>7928</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>7892</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>7912</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>7862</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>7962</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>7932</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>7862</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>7902</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>7912</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>7862</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>7828</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>7722</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>7852</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>7798</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>7762</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>11638</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>11462</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>11692</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>11638</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>11792</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>11438</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>11588</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>11652</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>11552</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>11188</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>10832</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>11402</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>10962</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>11362</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>11218</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>11262</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>10342</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>10992</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>10992</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>10568</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>11088</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>11222</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>10962</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>10588</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>10068</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>9828</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>10382</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>9772</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>9468</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>10268</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>9718</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>8952</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>10278</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>9382</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>8848</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>2092</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>2148</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2172</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>2222</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>3118</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>3312</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>3282</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>2988</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>3322</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>3662</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>3562</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>3648</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>3432</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>3778</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>2752</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>2732</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>2752</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2772</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>2762</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2338</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2372</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>2502</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>2422</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>2482</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>8248</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>7982</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>7662</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>8222</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>8132</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>8138</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>8128</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>8152</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>7958</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>7832</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>7838</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>8078</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>8142</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>8108</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>8158</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>8062</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>8122</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>8082</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>8062</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>8108</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>8058</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>8058</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>7888</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>7918</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>7968</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>7942</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>7912</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>12718</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>13098</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>13352</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>12718</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>13108</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>12452</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>12502</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>12828</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>12772</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>12618</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>13212</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>13512</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>12342</v>
+      </c>
+      <c r="C84" s="7" t="n">
         <v>12708</v>
       </c>
-      <c r="C24" s="6" t="n">
-        <v>11148</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>6308</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>QSRC=1</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>12788</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>11232</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>9392</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="D84" s="7" t="n">
+        <v>12762</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>9528</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>7808</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>8252</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>QSRC=2</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>10768</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>8358</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>8268</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G84" s="7" t="n">
+        <v>11862</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>12358</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>13092</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>10102</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>8368</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>8362</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B85" s="7" t="n">
+        <v>12388</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>12288</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>12602</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
-        <v>8862</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>8962</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>8358</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="G85" s="7" t="n">
+        <v>12062</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>12522</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>12452</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
-        <v>14382</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>12868</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>9058</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="B86" s="7" t="n">
+        <v>11938</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>11838</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>12258</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
-        <v>10642</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>14552</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>13978</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="G86" s="7" t="n">
+        <v>11672</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>12168</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>11918</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>10272</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>10688</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>14508</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="B87" s="7" t="n">
+        <v>11032</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>11192</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>11422</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>10278</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>9028</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>15088</v>
+      <c r="G87" s="7" t="n">
+        <v>11342</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>11408</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>11338</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1793,7 +4964,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1805,7 +4976,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1817,7 +4988,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1829,7 +5000,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:D28">
+  <conditionalFormatting sqref="B24:D29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1841,8 +5012,152 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:I28">
+  <conditionalFormatting sqref="G24:I29">
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:D69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:I69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D78">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:I78">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:D87">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:I87">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1864,7 +5179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1881,7 +5196,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legacy STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>Legacy STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -1895,461 +5210,1397 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>8358</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>11958</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>9778</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>2552</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2692</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2652</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>8358</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>11762</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>8832</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>2552</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>2678</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>12312</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>11242</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>11222</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>2718</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>2702</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2642</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>11578</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>10262</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>11532</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>2598</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>2838</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>11792</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>13472</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>11768</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>2542</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>2652</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2662</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>12168</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>13392</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>11712</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>2578</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>2682</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>9838</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>11822</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>11688</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>2608</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2682</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2652</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>9978</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>12558</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>11052</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>2628</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>2502</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>12178</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>11078</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>11632</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>2552</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2658</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2608</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>11238</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>9618</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>9268</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>2208</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2382</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>13162</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>10902</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>11158</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>2442</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2468</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2512</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>11398</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>11962</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>11862</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>2472</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2458</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>2592</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>10338</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>11938</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>10642</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>8182</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>8268</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>8232</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>10338</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>10638</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>10728</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>8182</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>8218</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>8392</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>12228</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>12348</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>12318</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>8242</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>8218</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>8212</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>10482</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>12568</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>8138</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>8458</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>8172</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>12228</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>11342</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>12292</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>8082</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>8158</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>8228</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>11698</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>12758</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>10612</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>8078</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>8248</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>8312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>13438</v>
-      </c>
-      <c r="C17" s="6" t="n">
+      <c r="B18" s="7" t="n">
+        <v>8198</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>8198</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>8162</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>8168</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>8092</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>8218</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>8088</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>7728</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>8008</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>8258</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>7978</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>7982</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>8028</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>7982</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>8068</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>8162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>11998</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>12258</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>12178</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>11998</v>
+      </c>
+      <c r="H24" s="7" t="n">
         <v>12188</v>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>10812</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="I24" s="7" t="n">
+        <v>12558</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>11922</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>11982</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>11982</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>11688</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>12408</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>11862</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>11502</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>11672</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>11882</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>11468</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>12022</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>11408</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>11618</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>12058</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>11712</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>11912</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>11838</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>11642</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>11252</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>11838</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>10498</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>10898</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>12588</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>11458</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>11828</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>11538</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>11352</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>10712</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>10538</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G28" s="7" t="n">
+        <v>10512</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>11222</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>11902</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>10258</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>9918</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>10932</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B29" s="7" t="n">
+        <v>11168</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>11272</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>11288</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>10572</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>11098</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>10348</v>
+      <c r="G29" s="7" t="n">
+        <v>11202</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>11358</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>11732</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>2858</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>2918</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>3098</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>2858</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>3082</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>2922</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>3052</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2958</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2822</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2992</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2802</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>2842</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>2838</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2982</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2808</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2778</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>2892</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>2742</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2828</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>2638</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2638</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2842</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>2598</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2862</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2568</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2642</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2802</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>8768</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>9168</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>9312</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>8768</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>9412</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>9422</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>8762</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>9202</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>8788</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>8512</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>8912</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>9458</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>8288</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>8662</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>8928</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>8528</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>9018</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>9452</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>8318</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>8682</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>9242</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>8318</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>8828</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>9292</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>8302</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>8542</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>8302</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>8158</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>8588</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>8672</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>8182</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>8348</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>8218</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>8452</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>8692</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>13152</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>13422</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>13802</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>13152</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>14088</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>13948</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>12812</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>13222</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>13082</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>12748</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>13178</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>13768</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>12302</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>12842</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>12792</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>12552</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>12952</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>13648</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>12168</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>12668</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>13048</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>12172</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>13038</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>13322</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>12198</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>12538</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>12462</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>11902</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>12638</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>12812</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>11712</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>12258</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>12238</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>11958</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>12592</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>12868</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2361,7 +6612,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2373,7 +6624,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2385,8 +6636,104 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:D29">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:I29">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
